--- a/fixtures/SUB_Y/submission.xlsx
+++ b/fixtures/SUB_Y/submission.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.7109375" customWidth="1" min="1" max="1"/>
@@ -626,62 +626,62 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Instructions</t>
+          <t>TPA basis</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fill the yellow cells with annual premiums per member greater than 0. Grey cells are referred. Do not insert, delete or rename sheets, rows or columns.</t>
+          <t>The rate in each TPA block is BEFORE the TPA factor: the issued TPA factor in Factor Tables is applied on top. Do not build the TPA difference into the block as well.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Template version</t>
+          <t>Instructions</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1 / generator ws0-1</t>
+          <t>Fill the yellow cells with annual premiums per member greater than 0. Grey cells are referred. Do not insert, delete or rename sheets, rows or columns.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Template version</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1 / generator ws0-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Structure hash</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>a5cc3bbbff4544408e647e19fa833066ddb52921c093d9af3d88eaa052486296</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Sheet directory</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Existing Rates</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>read only</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Factor Tables</t>
+          <t>Existing Rates</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Add-ons</t>
+          <t>Factor Tables</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -705,22 +705,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDIVIDUAL RGN_A</t>
+          <t>Add-ons</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fill yellow cells (3 block(s): TPA_RED, TPA_BLUE, TPA_GREEN)</t>
+          <t>read only</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>INDIVIDUAL RGN_A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fill yellow cells (3 block(s): TPA_RED, TPA_BLUE, TPA_GREEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Terms</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>fill</t>
         </is>
